--- a/data/equipment-labels.xlsx
+++ b/data/equipment-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,9 +416,1403 @@
         <v>Quantity</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AR 1102</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C2" t="str">
+        <v>AR 1102</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AR 3219</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AR 3219</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AR 3303</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AR 3303</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AR 3390</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C5" t="str">
+        <v>AR 3390</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AR 3415</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C6" t="str">
+        <v>AR 3415</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AR 3617</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C7" t="str">
+        <v>AR 3617</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AR 3632</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C8" t="str">
+        <v>AR 3632</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AR 3685</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C9" t="str">
+        <v>AR 3685</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AR 3692</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C10" t="str">
+        <v>AR 3692</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AR 3722</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C11" t="str">
+        <v>AR 3722</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AR 3824</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C12" t="str">
+        <v>AR 3824</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AR 4071</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C13" t="str">
+        <v>AR 4071</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AR 4083</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C14" t="str">
+        <v>AR 4083</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AR 4104</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C15" t="str">
+        <v>AR 4104</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AR 4123</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C16" t="str">
+        <v>AR 4123</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AR 4124</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C17" t="str">
+        <v>AR 4124</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AR 4134</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AR 4134</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AR 4276</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C19" t="str">
+        <v>AR 4276</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AR 4286</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C20" t="str">
+        <v>AR 4286</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AR 4288</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C21" t="str">
+        <v>AR 4288</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AR 4293</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C22" t="str">
+        <v>AR 4293</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AR 4296</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C23" t="str">
+        <v>AR 4296</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>AR 4298</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C24" t="str">
+        <v>AR 4298</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AR 4336</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C25" t="str">
+        <v>AR 4336</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>AR 4363</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C26" t="str">
+        <v>AR 4363</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>AR 4375</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C27" t="str">
+        <v>AR 4375</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>AR 4378</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C28" t="str">
+        <v>AR 4378</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>AR 4393</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C29" t="str">
+        <v>AR 4393</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>AR 4406</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C30" t="str">
+        <v>AR 4406</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>AR 4428</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C31" t="str">
+        <v>AR 4428</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>AR 4479</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C32" t="str">
+        <v>AR 4479</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>AR 4536</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C33" t="str">
+        <v>AR 4536</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>AR 4541</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C34" t="str">
+        <v>AR 4541</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>AR 4542</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C35" t="str">
+        <v>AR 4542</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>AR 4550</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C36" t="str">
+        <v>AR 4550</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>AR 4568</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C37" t="str">
+        <v>AR 4568</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>AR 4626</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C38" t="str">
+        <v>AR 4626</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>AR 4629</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C39" t="str">
+        <v>AR 4629</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>AR 4647</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C40" t="str">
+        <v>AR 4647</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>AR 4741</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C41" t="str">
+        <v>AR 4741</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>AR 4744</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C42" t="str">
+        <v>AR 4744</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>AR 4754</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C43" t="str">
+        <v>AR 4754</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>AR 4755</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C44" t="str">
+        <v>AR 4755</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>AR 4756</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C45" t="str">
+        <v>AR 4756</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>AR 4764</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C46" t="str">
+        <v>AR 4764</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>AR 4787</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C47" t="str">
+        <v>AR 4787</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>AR 4821</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C48" t="str">
+        <v>AR 4821</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>AR 4822</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C49" t="str">
+        <v>AR 4822</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>AR 4915</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C50" t="str">
+        <v>AR 4915</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>AR 4942</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C51" t="str">
+        <v>AR 4942</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AR 4947</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C52" t="str">
+        <v>AR 4947</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>AR 4957</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C53" t="str">
+        <v>AR 4957</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>AR 5012</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C54" t="str">
+        <v>AR 5012</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>AR 5086</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C55" t="str">
+        <v>AR 5086</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>AR 5110</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C56" t="str">
+        <v>AR 5110</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>AR 5111</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C57" t="str">
+        <v>AR 5111</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>AR 5112</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C58" t="str">
+        <v>AR 5112</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>AR 5152</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C59" t="str">
+        <v>AR 5152</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>AR 5173</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C60" t="str">
+        <v>AR 5173</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>AR 5260</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C61" t="str">
+        <v>AR 5260</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>AR 5267</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C62" t="str">
+        <v>AR 5267</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>AR 5268</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C63" t="str">
+        <v>AR 5268</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>AR 5328</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C64" t="str">
+        <v>AR 5328</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>AR 5342</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C65" t="str">
+        <v>AR 5342</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>AR 5343</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C66" t="str">
+        <v>AR 5343</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>AR 5439</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C67" t="str">
+        <v>AR 5439</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>AR 5440</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C68" t="str">
+        <v>AR 5440</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>AR 5495</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C69" t="str">
+        <v>AR 5495</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>AR 5496</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C70" t="str">
+        <v>AR 5496</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>AR 5497</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C71" t="str">
+        <v>AR 5497</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>AR 5507</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C72" t="str">
+        <v>AR 5507</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>AR 5518</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C73" t="str">
+        <v>AR 5518</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>AR 5520</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C74" t="str">
+        <v>AR 5520</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>AR 5633</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C75" t="str">
+        <v>AR 5633</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>AR 5634</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C76" t="str">
+        <v>AR 5634</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>AR 5635</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C77" t="str">
+        <v>AR 5635</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>AR 5673</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C78" t="str">
+        <v>AR 5673</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>AR 5862</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C79" t="str">
+        <v>AR 5862</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>AR 5888</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C80" t="str">
+        <v>AR 5888</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>AR 5962</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C81" t="str">
+        <v>AR 5962</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>AR 5967</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C82" t="str">
+        <v>AR 5967</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>AR 6011</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="C83" t="str">
+        <v>AR 6011</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Bulldog Forklifts</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E83"/>
   </ignoredErrors>
 </worksheet>
 </file>